--- a/research/CVT.NZ/Reports/CVT.NZ_DCF_Model.xlsx
+++ b/research/CVT.NZ/Reports/CVT.NZ_DCF_Model.xlsx
@@ -2355,9 +2355,10 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9">
-        <f> Owner FCF</f>
-        <v>0</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>= Owner FCF</t>
+        </is>
       </c>
       <c r="B9" s="5">
         <v>-27.227</v>
